--- a/UADE_PFI_Template-develop/Plan de Negocios/InfraEye - Flujo de Fondos y Evaluacion Economica.xlsx
+++ b/UADE_PFI_Template-develop/Plan de Negocios/InfraEye - Flujo de Fondos y Evaluacion Economica.xlsx
@@ -837,7 +837,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Desarrollo del MVP (2 desarrolladores, 6 meses)</t>
+          <t>Desarrollo del MVP (2 desarrolladores, 12 meses)</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
